--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-organization.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="452">
   <si>
     <t>Property</t>
   </si>
@@ -436,7 +436,7 @@
     <t>Organization.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -474,7 +474,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -508,7 +508,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -551,7 +551,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -694,6 +694,12 @@
   <si>
     <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-telematik-id}
 </t>
+  </si>
+  <si>
+    <t>An identifier intended for computation</t>
+  </si>
+  <si>
+    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
   </si>
   <si>
     <t>Organization.identifier:BSNR</t>
@@ -785,7 +791,7 @@
     <t>Used to categorize the organization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/organization-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -1239,7 +1245,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -1325,7 +1331,7 @@
     <t>The purpose for which you would contact a contact party.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
   </si>
   <si>
     <t>CE/CNE/CWE</t>
@@ -1414,7 +1420,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint|4.0.1)
+    <t xml:space="preserve">Reference(Endpoint)
 </t>
   </si>
   <si>
@@ -3739,7 +3745,7 @@
         <v>194</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3766,7 +3772,9 @@
       <c r="M18" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="N18" s="2"/>
+      <c r="N18" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3824,7 +3832,7 @@
         <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>116</v>
@@ -3833,7 +3841,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -4103,10 +4111,10 @@
         <v>216</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
@@ -4188,13 +4196,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>77</v>
@@ -4216,13 +4224,13 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
@@ -4304,13 +4312,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>77</v>
@@ -4332,13 +4340,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
@@ -4420,13 +4428,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -4448,13 +4456,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
@@ -4536,10 +4544,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4562,70 +4570,70 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="P25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q25" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="R25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="P25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q25" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="R25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4640,24 +4648,24 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4680,19 +4688,19 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4720,16 +4728,16 @@
         <v>156</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -4739,7 +4747,7 @@
         <v>114</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4754,27 +4762,27 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4796,19 +4804,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4833,11 +4841,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4855,7 +4865,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4870,27 +4880,27 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>77</v>
@@ -4912,19 +4922,19 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4949,11 +4959,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4971,7 +4983,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4986,24 +4998,24 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5029,16 +5041,16 @@
         <v>101</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5087,7 +5099,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5096,19 +5108,19 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5116,10 +5128,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5145,16 +5157,16 @@
         <v>101</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5203,7 +5215,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5221,7 +5233,7 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -5232,10 +5244,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5258,19 +5270,19 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5319,7 +5331,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5328,19 +5340,19 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5348,10 +5360,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5374,19 +5386,19 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5435,7 +5447,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5444,19 +5456,19 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5464,10 +5476,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5576,10 +5588,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5690,10 +5702,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5719,16 +5731,16 @@
         <v>166</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5741,7 +5753,7 @@
         <v>77</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>77</v>
@@ -5753,13 +5765,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5777,7 +5789,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5792,13 +5804,13 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5806,10 +5818,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5835,13 +5847,13 @@
         <v>166</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5855,7 +5867,7 @@
         <v>77</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>77</v>
@@ -5867,13 +5879,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5891,7 +5903,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5906,10 +5918,10 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5920,10 +5932,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5949,16 +5961,16 @@
         <v>101</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5971,7 +5983,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -6007,7 +6019,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6022,10 +6034,10 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6036,10 +6048,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6065,13 +6077,13 @@
         <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6085,7 +6097,7 @@
         <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>77</v>
@@ -6121,7 +6133,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6136,13 +6148,13 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6150,14 +6162,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6179,13 +6191,13 @@
         <v>101</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6199,7 +6211,7 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>77</v>
@@ -6235,7 +6247,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6250,13 +6262,13 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6264,14 +6276,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6293,13 +6305,13 @@
         <v>101</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6313,7 +6325,7 @@
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>77</v>
@@ -6349,7 +6361,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6364,10 +6376,10 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6378,14 +6390,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6407,13 +6419,13 @@
         <v>101</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6463,7 +6475,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6478,13 +6490,13 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6492,14 +6504,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6521,13 +6533,13 @@
         <v>101</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6541,7 +6553,7 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>77</v>
@@ -6577,7 +6589,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6592,13 +6604,13 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6606,10 +6618,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6635,13 +6647,13 @@
         <v>101</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6691,7 +6703,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6706,13 +6718,13 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6720,10 +6732,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6746,19 +6758,19 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6771,7 +6783,7 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>77</v>
@@ -6807,7 +6819,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6819,16 +6831,16 @@
         <v>149</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6836,10 +6848,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6862,19 +6874,19 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6923,7 +6935,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6935,13 +6947,13 @@
         <v>149</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>105</v>
@@ -6952,10 +6964,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6978,19 +6990,19 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7039,7 +7051,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7057,7 +7069,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7068,10 +7080,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7180,10 +7192,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7294,14 +7306,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7323,10 +7335,10 @@
         <v>108</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>111</v>
@@ -7381,7 +7393,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7410,10 +7422,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7436,19 +7448,19 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7476,10 +7488,10 @@
         <v>145</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7497,7 +7509,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7512,10 +7524,10 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7526,10 +7538,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7552,19 +7564,19 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7613,7 +7625,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7628,13 +7640,13 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7642,10 +7654,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7668,17 +7680,17 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7727,7 +7739,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7739,16 +7751,16 @@
         <v>149</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7756,10 +7768,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7782,19 +7794,19 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7843,7 +7855,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7858,13 +7870,13 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7872,10 +7884,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7898,19 +7910,19 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7959,7 +7971,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7971,13 +7983,13 @@
         <v>149</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-organization.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="450">
   <si>
     <t>Property</t>
   </si>
@@ -436,7 +436,7 @@
     <t>Organization.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -474,7 +474,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -508,7 +508,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -551,7 +551,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -694,12 +694,6 @@
   <si>
     <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-telematik-id}
 </t>
-  </si>
-  <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
   </si>
   <si>
     <t>Organization.identifier:BSNR</t>
@@ -791,7 +785,7 @@
     <t>Used to categorize the organization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
+    <t>http://hl7.org/fhir/ValueSet/organization-type|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -1245,7 +1239,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1331,7 +1325,7 @@
     <t>The purpose for which you would contact a contact party.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
   </si>
   <si>
     <t>CE/CNE/CWE</t>
@@ -1420,7 +1414,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -3745,7 +3739,7 @@
         <v>194</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3772,9 +3766,7 @@
       <c r="M18" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="N18" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3832,7 +3824,7 @@
         <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>116</v>
@@ -3841,7 +3833,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -4111,10 +4103,10 @@
         <v>216</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
@@ -4196,13 +4188,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>77</v>
@@ -4224,13 +4216,13 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
@@ -4312,13 +4304,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>77</v>
@@ -4340,13 +4332,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
@@ -4428,13 +4420,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>203</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -4456,13 +4448,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
@@ -4544,10 +4536,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4570,26 +4562,26 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="P25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q25" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="O25" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="P25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q25" t="s" s="2">
-        <v>234</v>
-      </c>
       <c r="R25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4633,7 +4625,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4648,24 +4640,24 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4688,19 +4680,19 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4728,16 +4720,16 @@
         <v>156</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB26" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -4747,7 +4739,7 @@
         <v>114</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4762,27 +4754,27 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4804,19 +4796,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4841,13 +4833,11 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4865,7 +4855,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4880,27 +4870,27 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>77</v>
@@ -4922,19 +4912,19 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4959,13 +4949,11 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4983,7 +4971,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4998,24 +4986,24 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5041,16 +5029,16 @@
         <v>101</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5099,7 +5087,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5108,19 +5096,19 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5128,10 +5116,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5157,16 +5145,16 @@
         <v>101</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5215,7 +5203,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5233,7 +5221,7 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -5244,10 +5232,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5270,19 +5258,19 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5331,7 +5319,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5340,19 +5328,19 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AK31" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AJ31" t="s" s="2">
+      <c r="AL31" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5360,10 +5348,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5386,19 +5374,19 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5447,7 +5435,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5456,19 +5444,19 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AJ32" t="s" s="2">
+      <c r="AL32" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AK32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5476,10 +5464,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5588,10 +5576,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5702,10 +5690,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5731,16 +5719,16 @@
         <v>166</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5753,43 +5741,43 @@
         <v>77</v>
       </c>
       <c r="T35" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="U35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="Y35" t="s" s="2">
+      <c r="AA35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5804,13 +5792,13 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5818,10 +5806,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5847,13 +5835,13 @@
         <v>166</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5867,43 +5855,43 @@
         <v>77</v>
       </c>
       <c r="T36" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="U36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="Y36" t="s" s="2">
+      <c r="AA36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5918,10 +5906,10 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5932,10 +5920,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5961,16 +5949,16 @@
         <v>101</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5983,7 +5971,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -6019,7 +6007,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6034,10 +6022,10 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6048,10 +6036,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6077,13 +6065,13 @@
         <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6097,7 +6085,7 @@
         <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>77</v>
@@ -6133,7 +6121,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6148,13 +6136,13 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6162,14 +6150,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6191,13 +6179,13 @@
         <v>101</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6211,7 +6199,7 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>77</v>
@@ -6247,7 +6235,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6262,13 +6250,13 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6276,14 +6264,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6305,13 +6293,13 @@
         <v>101</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6325,7 +6313,7 @@
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>77</v>
@@ -6361,7 +6349,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6376,10 +6364,10 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6390,14 +6378,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6419,13 +6407,13 @@
         <v>101</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6475,7 +6463,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6490,13 +6478,13 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6504,14 +6492,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6533,13 +6521,13 @@
         <v>101</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6553,7 +6541,7 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>77</v>
@@ -6589,7 +6577,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6604,13 +6592,13 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6618,10 +6606,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6647,13 +6635,13 @@
         <v>101</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6703,7 +6691,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6718,13 +6706,13 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6732,10 +6720,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6758,19 +6746,19 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6783,7 +6771,7 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>77</v>
@@ -6819,7 +6807,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6831,16 +6819,16 @@
         <v>149</v>
       </c>
       <c r="AJ44" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AK44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6848,10 +6836,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6874,19 +6862,19 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6935,7 +6923,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6947,13 +6935,13 @@
         <v>149</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>105</v>
@@ -6964,10 +6952,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6990,19 +6978,19 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7051,7 +7039,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7069,7 +7057,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7080,10 +7068,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7192,10 +7180,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7306,14 +7294,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7335,10 +7323,10 @@
         <v>108</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>111</v>
@@ -7393,7 +7381,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7422,10 +7410,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7448,19 +7436,19 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7488,10 +7476,10 @@
         <v>145</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7509,7 +7497,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7524,10 +7512,10 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7538,10 +7526,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7564,19 +7552,19 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7625,7 +7613,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7640,13 +7628,13 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7654,10 +7642,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7680,17 +7668,17 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7739,7 +7727,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7751,16 +7739,16 @@
         <v>149</v>
       </c>
       <c r="AJ52" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AK52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7768,10 +7756,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7794,19 +7782,19 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7855,7 +7843,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7870,13 +7858,13 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7884,10 +7872,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7910,19 +7898,19 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="N54" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7971,7 +7959,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7983,13 +7971,13 @@
         <v>149</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
